--- a/ABA_mining/outputs/eval/task3/staff/llama3.2/one_shot/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/staff/llama3.2/one_shot/Contrary(P)Body(N).xlsx
@@ -33651,10 +33651,10 @@
         <v>131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4680851063829787</v>
+        <v>0.468085</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.143791</v>
       </c>
       <c r="N2" t="n">
         <v>0.22</v>
@@ -33710,13 +33710,13 @@
         <v>131</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.458333</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.143791</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2189054726368159</v>
+        <v>0.218906</v>
       </c>
       <c r="O3" t="n">
         <v>0.6860000000000001</v>
@@ -33769,13 +33769,13 @@
         <v>131</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.458333</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.143791</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2189054726368159</v>
+        <v>0.218906</v>
       </c>
       <c r="O4" t="n">
         <v>0.6860000000000001</v>
